--- a/employment_xlsx/PECH_SCHEDULE_B_TEMPLATES.xlsx
+++ b/employment_xlsx/PECH_SCHEDULE_B_TEMPLATES.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,34 @@
       <i val="1"/>
       <color rgb="00999999"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000099CC"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00F5A623"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00888888"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00E8F4F8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="7"/>
     </font>
   </fonts>
   <fills count="8">
@@ -136,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -168,6 +196,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -242,6 +285,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="628650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -531,8 +604,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -547,51 +621,31 @@
     <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="6" customHeight="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="1" t="inlineStr"/>
-      <c r="C1" s="1" t="inlineStr"/>
-      <c r="D1" s="1" t="inlineStr"/>
-      <c r="E1" s="1" t="inlineStr"/>
-      <c r="F1" s="1" t="inlineStr"/>
-      <c r="G1" s="1" t="inlineStr"/>
-      <c r="H1" s="1" t="inlineStr"/>
-      <c r="I1" s="1" t="inlineStr"/>
-      <c r="J1" s="1" t="inlineStr"/>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>PECH GROUP HOLDINGS LTD</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SCHEDULE B: JOB DESCRIPTION &amp; KPIs</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="4" customHeight="1">
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="2" customHeight="1">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -600,418 +654,144 @@
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Confidential</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="8" customHeight="1"/>
+    <row r="7" ht="8" customHeight="1">
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+      <c r="G7" s="1" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr"/>
+      <c r="J7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SCHEDULE B: JOB DESCRIPTION &amp; KPIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Attached to Employment Contracts  |  CONFIDENTIAL</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="1" t="n"/>
-      <c r="H6" s="1" t="n"/>
-      <c r="I6" s="1" t="n"/>
-      <c r="J6" s="1" t="n"/>
-    </row>
-    <row r="7" ht="8" customHeight="1"/>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+      <c r="H12" s="1" t="n"/>
+      <c r="I12" s="1" t="n"/>
+      <c r="J12" s="1" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1"/>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  ALL ROLE KPI TEMPLATES (30 ROLES)</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Role ID</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Job Title</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>KPI 1</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>KPI 2</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>KPI 3</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>KPI 4</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>KPI 5</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>PECH-ENG-CTO-001</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>System uptime &gt;99.5%</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Sprint velocity +10%/quarter</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Hire pipeline filled</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>Security: 0 critical vulns</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>Tech debt &lt;15%</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>PECH-ENG-FS-001</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Full-Stack Engineer</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Feature delivery on sprint</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>Code review participation</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>Bug fix turnaround &lt;48h</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>Unit test coverage &gt;80%</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>Documentation updated</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>PECH-ENG-FE-001</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Frontend Engineer</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>Page load &lt;2s</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Lighthouse score &gt;90</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Cross-browser compat.</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>Accessibility WCAG AA</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>Component library growth</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>PECH-ENG-BE-001</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Backend Engineer</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>API response &lt;200ms p95</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>Zero downtime deploys</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>Error rate &lt;0.1%</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>Database query optimized</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>API documentation 100%</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>PECH-ENG-IOT-001</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>IoT Engineer</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>Device connectivity &gt;98%</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>Firmware OTA success &gt;99%</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>Sensor accuracy ±2%</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>Battery life targets met</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Certification compliance</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>PECH-ENG-MOB-001</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Mobile Engineer</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>App store rating &gt;4.5</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Crash-free rate &gt;99.5%</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>App load &lt;3s</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>Feature parity web/mobile</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>User retention +5%/month</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>PECH-ENG-DEV-001</t>
+          <t>PECH-ENG-CTO-001</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -1021,27 +801,27 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>CI/CD pipeline &lt;10min</t>
+          <t>System uptime &gt;99.5%</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>Infrastructure cost -10%</t>
+          <t>Sprint velocity +10%/quarter</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Incident response &lt;15min</t>
+          <t>Hire pipeline filled</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Backup/restore tested monthly</t>
+          <t>Security: 0 critical vulns</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>Security patches &lt;24h</t>
+          <t>Tech debt &lt;15%</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
@@ -1052,16 +832,16 @@
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>PECH-ENG-DATA-001</t>
+          <t>PECH-ENG-FS-001</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1071,27 +851,27 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Data pipeline uptime &gt;99%</t>
+          <t>Feature delivery on sprint</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Query performance SLA met</t>
+          <t>Code review participation</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>ML model accuracy targets</t>
+          <t>Bug fix turnaround &lt;48h</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Data quality score &gt;95%</t>
+          <t>Unit test coverage &gt;80%</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>Cost per inference -15%</t>
+          <t>Documentation updated</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
@@ -1102,16 +882,16 @@
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>PECH-ENG-DATA-002</t>
+          <t>PECH-ENG-FE-001</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Frontend Engineer</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -1121,27 +901,27 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>Weekly reports on time</t>
+          <t>Page load &lt;2s</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>Dashboard uptime &gt;99%</t>
+          <t>Lighthouse score &gt;90</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Insight accuracy verified</t>
+          <t>Cross-browser compat.</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Stakeholder satisfaction &gt;4/5</t>
+          <t>Accessibility WCAG AA</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>Self-service adoption +20%</t>
+          <t>Component library growth</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
@@ -1152,16 +932,16 @@
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>PECH-ENG-QA-001</t>
+          <t>PECH-ENG-BE-001</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1171,27 +951,27 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Test coverage &gt;85%</t>
+          <t>API response &lt;200ms p95</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Bug escape rate &lt;5%</t>
+          <t>Zero downtime deploys</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Regression suite pass rate</t>
+          <t>Error rate &lt;0.1%</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Test automation +20%/qtr</t>
+          <t>Database query optimized</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>Release go/no-go accuracy</t>
+          <t>API documentation 100%</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
@@ -1202,46 +982,46 @@
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>PECH-DES-UI-001</t>
+          <t>PECH-ENG-IOT-001</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>UI/UX Designer</t>
+          <t>IoT Engineer</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Design system components</t>
+          <t>Device connectivity &gt;98%</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>User task success &gt;90%</t>
+          <t>Firmware OTA success &gt;99%</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Prototype turnaround &lt;3d</t>
+          <t>Sensor accuracy ±2%</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Usability test score &gt;80</t>
+          <t>Battery life targets met</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>Brand consistency 100%</t>
+          <t>Certification compliance</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
@@ -1252,46 +1032,46 @@
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>PECH-DES-GRA-001</t>
+          <t>PECH-ENG-MOB-001</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Graphic Designer</t>
+          <t>Mobile Engineer</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Asset turnaround &lt;2d</t>
+          <t>App store rating &gt;4.5</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>Brand guideline adherence</t>
+          <t>Crash-free rate &gt;99.5%</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Social media engagement</t>
+          <t>App load &lt;3s</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Print quality 100%</t>
+          <t>Feature parity web/mobile</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>Template library growth</t>
+          <t>User retention +5%/month</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
@@ -1302,46 +1082,46 @@
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>PECH-BIZ-PM-001</t>
+          <t>PECH-ENG-DEV-001</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Payments PM</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Product &amp; Business</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>PSSP licence milestones</t>
+          <t>CI/CD pipeline &lt;10min</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>Transaction success &gt;99.5%</t>
+          <t>Infrastructure cost -10%</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Feature adoption rate</t>
+          <t>Incident response &lt;15min</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Stakeholder NPS &gt;8</t>
+          <t>Backup/restore tested monthly</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Regulatory compliance 100%</t>
+          <t>Security patches &lt;24h</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
@@ -1352,46 +1132,46 @@
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>PECH-BIZ-BD-001</t>
+          <t>PECH-ENG-DATA-001</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>BD Lead</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Product &amp; Business</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Pipeline value target</t>
+          <t>Data pipeline uptime &gt;99%</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>Conversion rate &gt;15%</t>
+          <t>Query performance SLA met</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Partnership agreements</t>
+          <t>ML model accuracy targets</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Revenue growth targets</t>
+          <t>Data quality score &gt;95%</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>Client retention &gt;90%</t>
+          <t>Cost per inference -15%</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
@@ -1402,46 +1182,46 @@
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>PECH-BIZ-MKT-001</t>
+          <t>PECH-ENG-DATA-002</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Market Ops Manager</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Product &amp; Business</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>Vendor onboarding target</t>
+          <t>Weekly reports on time</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>GMV growth monthly</t>
+          <t>Dashboard uptime &gt;99%</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Market coverage expansion</t>
+          <t>Insight accuracy verified</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Vendor satisfaction &gt;4/5</t>
+          <t>Stakeholder satisfaction &gt;4/5</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>Operational cost ratio</t>
+          <t>Self-service adoption +20%</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
@@ -1452,46 +1232,46 @@
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>PECH-BIZ-COMP-001</t>
+          <t>PECH-ENG-QA-001</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Compliance Officer</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Product &amp; Business</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Regulatory filings on time</t>
+          <t>Test coverage &gt;85%</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Audit findings resolved</t>
+          <t>Bug escape rate &lt;5%</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Policy update cadence</t>
+          <t>Regression suite pass rate</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Training completion 100%</t>
+          <t>Test automation +20%/qtr</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>Zero compliance breaches</t>
+          <t>Release go/no-go accuracy</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -1502,46 +1282,46 @@
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>PECH-OPS-LOG-001</t>
+          <t>PECH-DES-UI-001</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Logistics Coordinator</t>
+          <t>UI/UX Designer</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>Delivery SLA &gt;95%</t>
+          <t>Design system components</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>Cost per delivery -10%</t>
+          <t>User task success &gt;90%</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Route optimization savings</t>
+          <t>Prototype turnaround &lt;3d</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Damage rate &lt;1%</t>
+          <t>Usability test score &gt;80</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>Driver utilization &gt;85%</t>
+          <t>Brand consistency 100%</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
@@ -1552,46 +1332,46 @@
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>PECH-OPS-CS-001</t>
+          <t>PECH-DES-GRA-001</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>CS Lead</t>
+          <t>Graphic Designer</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>First response &lt;1h</t>
+          <t>Asset turnaround &lt;2d</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>Resolution time &lt;24h</t>
+          <t>Brand guideline adherence</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>CSAT score &gt;4.5/5</t>
+          <t>Social media engagement</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Ticket backlog &lt;20</t>
+          <t>Print quality 100%</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>Team training hours/month</t>
+          <t>Template library growth</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
@@ -1602,46 +1382,46 @@
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>PECH-OPS-CS-002</t>
+          <t>PECH-BIZ-PM-001</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>CS Rep</t>
+          <t>Payments PM</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Product &amp; Business</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>Tickets resolved/day &gt;15</t>
+          <t>PSSP licence milestones</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>CSAT per agent &gt;4/5</t>
+          <t>Transaction success &gt;99.5%</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>First contact resolution &gt;70%</t>
+          <t>Feature adoption rate</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Knowledge base updates</t>
+          <t>Stakeholder NPS &gt;8</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>Escalation rate &lt;10%</t>
+          <t>Regulatory compliance 100%</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
@@ -1652,141 +1432,357 @@
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>PECH-BIZ-BD-001</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>BD Lead</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Product &amp; Business</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Pipeline value target</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Conversion rate &gt;15%</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>Partnership agreements</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Revenue growth targets</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>Client retention &gt;90%</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>PECH-BIZ-MKT-001</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Market Ops Manager</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Product &amp; Business</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Vendor onboarding target</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>GMV growth monthly</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Market coverage expansion</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Vendor satisfaction &gt;4/5</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Operational cost ratio</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>PECH-BIZ-COMP-001</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Compliance Officer</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Product &amp; Business</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Regulatory filings on time</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Audit findings resolved</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>Policy update cadence</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Training completion 100%</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>Zero compliance breaches</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>PECH-OPS-LOG-001</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Logistics Coordinator</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Delivery SLA &gt;95%</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Cost per delivery -10%</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Route optimization savings</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Damage rate &lt;1%</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Driver utilization &gt;85%</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>PECH-OPS-CS-001</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>CS Lead</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>First response &lt;1h</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Resolution time &lt;24h</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>CSAT score &gt;4.5/5</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Ticket backlog &lt;20</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>Team training hours/month</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>PECH-OPS-CS-002</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>CS Rep</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Tickets resolved/day &gt;15</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>CSAT per agent &gt;4/5</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>First contact resolution &gt;70%</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Knowledge base updates</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Escalation rate &lt;10%</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>PECH-OPS-FIN-001</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>Finance Officer</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Books closed by 5th</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Reconciliation accuracy</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>Expense report turnaround</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>Audit-ready at all times</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>Cash flow forecast accuracy</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J35" s="11" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
-      <c r="J30" s="12" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
-      <c r="H31" s="12" t="n"/>
-      <c r="I31" s="12" t="n"/>
-      <c r="J31" s="12" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="12" t="n"/>
-      <c r="J32" s="12" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="12" t="n"/>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="12" t="n"/>
-      <c r="J33" s="12" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="12" t="n"/>
-      <c r="H34" s="12" t="n"/>
-      <c r="I34" s="12" t="n"/>
-      <c r="J34" s="12" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="12" t="n"/>
-      <c r="H35" s="12" t="n"/>
-      <c r="I35" s="12" t="n"/>
-      <c r="J35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B36" s="12" t="n"/>
       <c r="C36" s="12" t="n"/>
@@ -1800,7 +1796,7 @@
     </row>
     <row r="37">
       <c r="A37" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B37" s="12" t="n"/>
       <c r="C37" s="12" t="n"/>
@@ -1814,7 +1810,7 @@
     </row>
     <row r="38">
       <c r="A38" s="12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B38" s="12" t="n"/>
       <c r="C38" s="12" t="n"/>
@@ -1828,7 +1824,7 @@
     </row>
     <row r="39">
       <c r="A39" s="12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B39" s="12" t="n"/>
       <c r="C39" s="12" t="n"/>
@@ -1840,51 +1836,170 @@
       <c r="I39" s="12" t="n"/>
       <c r="J39" s="12" t="n"/>
     </row>
+    <row r="40">
+      <c r="A40" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="12" t="n"/>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="12" t="n"/>
+      <c r="G40" s="12" t="n"/>
+      <c r="H40" s="12" t="n"/>
+      <c r="I40" s="12" t="n"/>
+      <c r="J40" s="12" t="n"/>
+    </row>
     <row r="41" ht="3" customHeight="1">
-      <c r="A41" s="5" t="n"/>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
+      <c r="A41" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="B41" s="12" t="n"/>
+      <c r="C41" s="12" t="n"/>
+      <c r="D41" s="12" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="12" t="n"/>
+      <c r="G41" s="12" t="n"/>
+      <c r="H41" s="12" t="n"/>
+      <c r="I41" s="12" t="n"/>
+      <c r="J41" s="12" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="12" t="n"/>
+      <c r="J42" s="12" t="n"/>
+    </row>
+    <row r="43" ht="3" customHeight="1">
+      <c r="A43" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B43" s="12" t="n"/>
+      <c r="C43" s="12" t="n"/>
+      <c r="D43" s="12" t="n"/>
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="12" t="n"/>
+      <c r="G43" s="12" t="n"/>
+      <c r="H43" s="12" t="n"/>
+      <c r="I43" s="12" t="n"/>
+      <c r="J43" s="12" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="B44" s="12" t="n"/>
+      <c r="C44" s="12" t="n"/>
+      <c r="D44" s="12" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="12" t="n"/>
+      <c r="G44" s="12" t="n"/>
+      <c r="H44" s="12" t="n"/>
+      <c r="I44" s="12" t="n"/>
+      <c r="J44" s="12" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="12" t="n"/>
+      <c r="D45" s="12" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="12" t="n"/>
+      <c r="G45" s="12" t="n"/>
+      <c r="H45" s="12" t="n"/>
+      <c r="I45" s="12" t="n"/>
+      <c r="J45" s="12" t="n"/>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n"/>
-      <c r="C42" s="14" t="n"/>
-      <c r="D42" s="14" t="n"/>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="14" t="n"/>
-      <c r="G42" s="14" t="n"/>
-      <c r="H42" s="14" t="n"/>
-      <c r="I42" s="14" t="n"/>
-      <c r="J42" s="14" t="n"/>
-    </row>
-    <row r="43" ht="3" customHeight="1">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="1" t="n"/>
-      <c r="C43" s="1" t="n"/>
-      <c r="D43" s="1" t="n"/>
-      <c r="E43" s="1" t="n"/>
-      <c r="F43" s="1" t="n"/>
-      <c r="G43" s="1" t="n"/>
-      <c r="H43" s="1" t="n"/>
-      <c r="I43" s="1" t="n"/>
-      <c r="J43" s="1" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n"/>
+      <c r="B49" s="1" t="n"/>
+      <c r="C49" s="1" t="n"/>
+      <c r="D49" s="1" t="n"/>
+      <c r="E49" s="1" t="n"/>
+      <c r="F49" s="1" t="n"/>
+      <c r="G49" s="1" t="n"/>
+      <c r="H49" s="1" t="n"/>
+      <c r="I49" s="1" t="n"/>
+      <c r="J49" s="1" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>Confidential — PECH Group Holdings Ltd — Lagos, Nigeria — pechgroupholdings.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n"/>
+      <c r="B55" s="1" t="n"/>
+      <c r="C55" s="1" t="n"/>
+      <c r="D55" s="1" t="n"/>
+      <c r="E55" s="1" t="n"/>
+      <c r="F55" s="1" t="n"/>
+      <c r="G55" s="1" t="n"/>
+      <c r="H55" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A53:H53"/>
     <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A51:H51"/>
     <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A42:J42"/>
   </mergeCells>
@@ -1895,5 +2010,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;8 PECH Group Holdings Ltd | Confidential</oddHeader>
+    <oddFooter>&amp;C&amp;7 PECH Group Holdings Ltd | Lagos, Nigeria | pechgroupholdings.tech</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/employment_xlsx/PECH_SCHEDULE_B_TEMPLATES.xlsx
+++ b/employment_xlsx/PECH_SCHEDULE_B_TEMPLATES.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,34 +64,6 @@
       <i val="1"/>
       <color rgb="00999999"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="000099CC"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <i val="1"/>
-      <color rgb="00F5A623"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="00888888"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00E8F4F8"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="00AAAAAA"/>
-      <sz val="7"/>
     </font>
   </fonts>
   <fills count="8">
@@ -164,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -196,21 +168,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -285,36 +242,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="628650"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -606,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -621,31 +548,51 @@
     <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr"/>
+      <c r="I1" s="1" t="inlineStr"/>
+      <c r="J1" s="1" t="inlineStr"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>PECH GROUP HOLDINGS LTD</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="2" customHeight="1">
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SCHEDULE B: JOB DESCRIPTION &amp; KPIs</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="4" customHeight="1">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -654,144 +601,418 @@
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Confidential</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="8" customHeight="1"/>
-    <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="1" t="inlineStr"/>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr"/>
-      <c r="F7" s="1" t="inlineStr"/>
-      <c r="G7" s="1" t="inlineStr"/>
-      <c r="H7" s="1" t="inlineStr"/>
-      <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr"/>
-    </row>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Attached to Employment Contracts  |  CONFIDENTIAL</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="4" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="1" t="n"/>
+      <c r="G6" s="1" t="n"/>
+      <c r="H6" s="1" t="n"/>
+      <c r="I6" s="1" t="n"/>
+      <c r="J6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="8" customHeight="1"/>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ALL ROLE KPI TEMPLATES (30 ROLES)</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SCHEDULE B: JOB DESCRIPTION &amp; KPIs</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Role ID</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Job Title</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>KPI 1</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>KPI 2</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>KPI 3</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>KPI 4</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>KPI 5</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
+      <c r="A10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>PECH-ENG-CTO-001</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>System uptime &gt;99.5%</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Sprint velocity +10%/quarter</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Hire pipeline filled</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Security: 0 critical vulns</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Tech debt &lt;15%</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Attached to Employment Contracts  |  CONFIDENTIAL</t>
+      <c r="A11" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>PECH-ENG-FS-001</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Feature delivery on sprint</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Code review participation</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Bug fix turnaround &lt;48h</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Unit test coverage &gt;80%</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>Documentation updated</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="1" t="n"/>
-      <c r="G12" s="1" t="n"/>
-      <c r="H12" s="1" t="n"/>
-      <c r="I12" s="1" t="n"/>
-      <c r="J12" s="1" t="n"/>
-    </row>
-    <row r="13" ht="28" customHeight="1"/>
+      <c r="A12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>PECH-ENG-FE-001</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Frontend Engineer</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Page load &lt;2s</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Lighthouse score &gt;90</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Cross-browser compat.</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Accessibility WCAG AA</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Component library growth</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>PECH-ENG-BE-001</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>API response &lt;200ms p95</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Zero downtime deploys</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>Error rate &lt;0.1%</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Database query optimized</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>API documentation 100%</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ALL ROLE KPI TEMPLATES (30 ROLES)</t>
+      <c r="A14" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>PECH-ENG-IOT-001</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>IoT Engineer</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Device connectivity &gt;98%</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Firmware OTA success &gt;99%</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Sensor accuracy ±2%</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Battery life targets met</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Certification compliance</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Role ID</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Job Title</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>KPI 1</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>KPI 2</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>KPI 3</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>KPI 4</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>KPI 5</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="A15" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>PECH-ENG-MOB-001</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Mobile Engineer</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>App store rating &gt;4.5</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Crash-free rate &gt;99.5%</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>App load &lt;3s</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Feature parity web/mobile</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>User retention +5%/month</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>PECH-ENG-CTO-001</t>
+          <t>PECH-ENG-DEV-001</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -801,27 +1022,27 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>System uptime &gt;99.5%</t>
+          <t>CI/CD pipeline &lt;10min</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>Sprint velocity +10%/quarter</t>
+          <t>Infrastructure cost -10%</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Hire pipeline filled</t>
+          <t>Incident response &lt;15min</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Security: 0 critical vulns</t>
+          <t>Backup/restore tested monthly</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>Tech debt &lt;15%</t>
+          <t>Security patches &lt;24h</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
@@ -832,16 +1053,16 @@
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>PECH-ENG-FS-001</t>
+          <t>PECH-ENG-DATA-001</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -851,27 +1072,27 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Feature delivery on sprint</t>
+          <t>Data pipeline uptime &gt;99%</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Code review participation</t>
+          <t>Query performance SLA met</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>Bug fix turnaround &lt;48h</t>
+          <t>ML model accuracy targets</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Unit test coverage &gt;80%</t>
+          <t>Data quality score &gt;95%</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>Documentation updated</t>
+          <t>Cost per inference -15%</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
@@ -882,16 +1103,16 @@
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>PECH-ENG-FE-001</t>
+          <t>PECH-ENG-DATA-002</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -901,27 +1122,27 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>Page load &lt;2s</t>
+          <t>Weekly reports on time</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>Lighthouse score &gt;90</t>
+          <t>Dashboard uptime &gt;99%</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Cross-browser compat.</t>
+          <t>Insight accuracy verified</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Accessibility WCAG AA</t>
+          <t>Stakeholder satisfaction &gt;4/5</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>Component library growth</t>
+          <t>Self-service adoption +20%</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
@@ -932,16 +1153,16 @@
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>PECH-ENG-BE-001</t>
+          <t>PECH-ENG-QA-001</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -951,27 +1172,27 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>API response &lt;200ms p95</t>
+          <t>Test coverage &gt;85%</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Zero downtime deploys</t>
+          <t>Bug escape rate &lt;5%</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Error rate &lt;0.1%</t>
+          <t>Regression suite pass rate</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Database query optimized</t>
+          <t>Test automation +20%/qtr</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>API documentation 100%</t>
+          <t>Release go/no-go accuracy</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
@@ -982,46 +1203,46 @@
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>PECH-ENG-IOT-001</t>
+          <t>PECH-DES-UI-001</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>IoT Engineer</t>
+          <t>UI/UX Designer</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Device connectivity &gt;98%</t>
+          <t>Design system components</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>Firmware OTA success &gt;99%</t>
+          <t>User task success &gt;90%</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Sensor accuracy ±2%</t>
+          <t>Prototype turnaround &lt;3d</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Battery life targets met</t>
+          <t>Usability test score &gt;80</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>Certification compliance</t>
+          <t>Brand consistency 100%</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
@@ -1032,46 +1253,46 @@
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>PECH-ENG-MOB-001</t>
+          <t>PECH-DES-GRA-001</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Mobile Engineer</t>
+          <t>Graphic Designer</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>App store rating &gt;4.5</t>
+          <t>Asset turnaround &lt;2d</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>Crash-free rate &gt;99.5%</t>
+          <t>Brand guideline adherence</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>App load &lt;3s</t>
+          <t>Social media engagement</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Feature parity web/mobile</t>
+          <t>Print quality 100%</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>User retention +5%/month</t>
+          <t>Template library growth</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
@@ -1082,46 +1303,46 @@
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>PECH-ENG-DEV-001</t>
+          <t>PECH-BIZ-PM-001</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Payments PM</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Product &amp; Business</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>CI/CD pipeline &lt;10min</t>
+          <t>PSSP licence milestones</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>Infrastructure cost -10%</t>
+          <t>Transaction success &gt;99.5%</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Incident response &lt;15min</t>
+          <t>Feature adoption rate</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Backup/restore tested monthly</t>
+          <t>Stakeholder NPS &gt;8</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Security patches &lt;24h</t>
+          <t>Regulatory compliance 100%</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
@@ -1132,46 +1353,46 @@
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>PECH-ENG-DATA-001</t>
+          <t>PECH-BIZ-BD-001</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>BD Lead</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Product &amp; Business</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Data pipeline uptime &gt;99%</t>
+          <t>Pipeline value target</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>Query performance SLA met</t>
+          <t>Conversion rate &gt;15%</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>ML model accuracy targets</t>
+          <t>Partnership agreements</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Data quality score &gt;95%</t>
+          <t>Revenue growth targets</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>Cost per inference -15%</t>
+          <t>Client retention &gt;90%</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
@@ -1182,46 +1403,46 @@
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>PECH-ENG-DATA-002</t>
+          <t>PECH-BIZ-MKT-001</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Market Ops Manager</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Product &amp; Business</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>Weekly reports on time</t>
+          <t>Vendor onboarding target</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Dashboard uptime &gt;99%</t>
+          <t>GMV growth monthly</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Insight accuracy verified</t>
+          <t>Market coverage expansion</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Stakeholder satisfaction &gt;4/5</t>
+          <t>Vendor satisfaction &gt;4/5</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>Self-service adoption +20%</t>
+          <t>Operational cost ratio</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
@@ -1232,46 +1453,46 @@
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>PECH-ENG-QA-001</t>
+          <t>PECH-BIZ-COMP-001</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Compliance Officer</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Product &amp; Business</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Test coverage &gt;85%</t>
+          <t>Regulatory filings on time</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Bug escape rate &lt;5%</t>
+          <t>Audit findings resolved</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Regression suite pass rate</t>
+          <t>Policy update cadence</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Test automation +20%/qtr</t>
+          <t>Training completion 100%</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>Release go/no-go accuracy</t>
+          <t>Zero compliance breaches</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -1282,46 +1503,46 @@
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>PECH-DES-UI-001</t>
+          <t>PECH-OPS-LOG-001</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>UI/UX Designer</t>
+          <t>Logistics Coordinator</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>Design system components</t>
+          <t>Delivery SLA &gt;95%</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>User task success &gt;90%</t>
+          <t>Cost per delivery -10%</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Prototype turnaround &lt;3d</t>
+          <t>Route optimization savings</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Usability test score &gt;80</t>
+          <t>Damage rate &lt;1%</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>Brand consistency 100%</t>
+          <t>Driver utilization &gt;85%</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
@@ -1332,46 +1553,46 @@
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="11" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>PECH-DES-GRA-001</t>
+          <t>PECH-OPS-CS-001</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Graphic Designer</t>
+          <t>CS Lead</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Asset turnaround &lt;2d</t>
+          <t>First response &lt;1h</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>Brand guideline adherence</t>
+          <t>Resolution time &lt;24h</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Social media engagement</t>
+          <t>CSAT score &gt;4.5/5</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Print quality 100%</t>
+          <t>Ticket backlog &lt;20</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>Template library growth</t>
+          <t>Team training hours/month</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
@@ -1382,46 +1603,46 @@
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>PECH-BIZ-PM-001</t>
+          <t>PECH-OPS-CS-002</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Payments PM</t>
+          <t>CS Rep</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Product &amp; Business</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>PSSP licence milestones</t>
+          <t>Tickets resolved/day &gt;15</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Transaction success &gt;99.5%</t>
+          <t>CSAT per agent &gt;4/5</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Feature adoption rate</t>
+          <t>First contact resolution &gt;70%</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Stakeholder NPS &gt;8</t>
+          <t>Knowledge base updates</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>Regulatory compliance 100%</t>
+          <t>Escalation rate &lt;10%</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
@@ -1432,46 +1653,46 @@
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>PECH-BIZ-BD-001</t>
+          <t>PECH-OPS-FIN-001</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>BD Lead</t>
+          <t>Finance Officer</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Product &amp; Business</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Pipeline value target</t>
+          <t>Books closed by 5th</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>Conversion rate &gt;15%</t>
+          <t>Reconciliation accuracy</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Partnership agreements</t>
+          <t>Expense report turnaround</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Revenue growth targets</t>
+          <t>Audit-ready at all times</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>Client retention &gt;90%</t>
+          <t>Cash flow forecast accuracy</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
@@ -1481,308 +1702,92 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>PECH-BIZ-MKT-001</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Market Ops Manager</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>Product &amp; Business</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>Vendor onboarding target</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>GMV growth monthly</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>Market coverage expansion</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>Vendor satisfaction &gt;4/5</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>Operational cost ratio</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
+      <c r="A30" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>PECH-BIZ-COMP-001</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>Compliance Officer</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>Product &amp; Business</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Regulatory filings on time</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>Audit findings resolved</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>Policy update cadence</t>
-        </is>
-      </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>Training completion 100%</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>Zero compliance breaches</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
+      <c r="A31" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>PECH-OPS-LOG-001</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>Logistics Coordinator</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>Delivery SLA &gt;95%</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>Cost per delivery -10%</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>Route optimization savings</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>Damage rate &lt;1%</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>Driver utilization &gt;85%</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
+      <c r="A32" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>PECH-OPS-CS-001</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>CS Lead</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>First response &lt;1h</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>Resolution time &lt;24h</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>CSAT score &gt;4.5/5</t>
-        </is>
-      </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>Ticket backlog &lt;20</t>
-        </is>
-      </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>Team training hours/month</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
+      <c r="A33" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>PECH-OPS-CS-002</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>CS Rep</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>Tickets resolved/day &gt;15</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>CSAT per agent &gt;4/5</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>First contact resolution &gt;70%</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>Knowledge base updates</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Escalation rate &lt;10%</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
+      <c r="A34" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>PECH-OPS-FIN-001</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>Finance Officer</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Books closed by 5th</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>Reconciliation accuracy</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>Expense report turnaround</t>
-        </is>
-      </c>
-      <c r="H35" s="11" t="inlineStr">
-        <is>
-          <t>Audit-ready at all times</t>
-        </is>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>Cash flow forecast accuracy</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
+      <c r="A35" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B36" s="12" t="n"/>
       <c r="C36" s="12" t="n"/>
@@ -1796,7 +1801,7 @@
     </row>
     <row r="37">
       <c r="A37" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B37" s="12" t="n"/>
       <c r="C37" s="12" t="n"/>
@@ -1810,7 +1815,7 @@
     </row>
     <row r="38">
       <c r="A38" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B38" s="12" t="n"/>
       <c r="C38" s="12" t="n"/>
@@ -1824,7 +1829,7 @@
     </row>
     <row r="39">
       <c r="A39" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B39" s="12" t="n"/>
       <c r="C39" s="12" t="n"/>
@@ -1836,170 +1841,51 @@
       <c r="I39" s="12" t="n"/>
       <c r="J39" s="12" t="n"/>
     </row>
-    <row r="40">
-      <c r="A40" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="12" t="n"/>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="12" t="n"/>
-      <c r="J40" s="12" t="n"/>
-    </row>
     <row r="41" ht="3" customHeight="1">
-      <c r="A41" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="12" t="n"/>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="n"/>
-      <c r="I41" s="12" t="n"/>
-      <c r="J41" s="12" t="n"/>
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12" t="n"/>
-      <c r="E42" s="12" t="n"/>
-      <c r="F42" s="12" t="n"/>
-      <c r="G42" s="12" t="n"/>
-      <c r="H42" s="12" t="n"/>
-      <c r="I42" s="12" t="n"/>
-      <c r="J42" s="12" t="n"/>
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="14" t="n"/>
+      <c r="H42" s="14" t="n"/>
+      <c r="I42" s="14" t="n"/>
+      <c r="J42" s="14" t="n"/>
     </row>
     <row r="43" ht="3" customHeight="1">
-      <c r="A43" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="n"/>
-      <c r="H43" s="12" t="n"/>
-      <c r="I43" s="12" t="n"/>
-      <c r="J43" s="12" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="12" t="n"/>
-      <c r="G44" s="12" t="n"/>
-      <c r="H44" s="12" t="n"/>
-      <c r="I44" s="12" t="n"/>
-      <c r="J44" s="12" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="12" t="n"/>
-      <c r="G45" s="12" t="n"/>
-      <c r="H45" s="12" t="n"/>
-      <c r="I45" s="12" t="n"/>
-      <c r="J45" s="12" t="n"/>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="5" t="n"/>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n"/>
-      <c r="B49" s="1" t="n"/>
-      <c r="C49" s="1" t="n"/>
-      <c r="D49" s="1" t="n"/>
-      <c r="E49" s="1" t="n"/>
-      <c r="F49" s="1" t="n"/>
-      <c r="G49" s="1" t="n"/>
-      <c r="H49" s="1" t="n"/>
-      <c r="I49" s="1" t="n"/>
-      <c r="J49" s="1" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="18" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="18" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="18" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="19" t="inlineStr">
-        <is>
-          <t>Confidential — PECH Group Holdings Ltd — Lagos, Nigeria — pechgroupholdings.tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n"/>
-      <c r="B55" s="1" t="n"/>
-      <c r="C55" s="1" t="n"/>
-      <c r="D55" s="1" t="n"/>
-      <c r="E55" s="1" t="n"/>
-      <c r="F55" s="1" t="n"/>
-      <c r="G55" s="1" t="n"/>
-      <c r="H55" s="1" t="n"/>
+      <c r="A43" s="1" t="n"/>
+      <c r="B43" s="1" t="n"/>
+      <c r="C43" s="1" t="n"/>
+      <c r="D43" s="1" t="n"/>
+      <c r="E43" s="1" t="n"/>
+      <c r="F43" s="1" t="n"/>
+      <c r="G43" s="1" t="n"/>
+      <c r="H43" s="1" t="n"/>
+      <c r="I43" s="1" t="n"/>
+      <c r="J43" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="5">
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A53:H53"/>
     <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A51:H51"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A42:J42"/>
   </mergeCells>
@@ -2009,15 +1895,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;8 PECH Group Holdings Ltd | Confidential</oddHeader>
-    <oddFooter>&amp;C&amp;7 PECH Group Holdings Ltd | Lagos, Nigeria | pechgroupholdings.tech</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/employment_xlsx/PECH_SCHEDULE_B_TEMPLATES.xlsx
+++ b/employment_xlsx/PECH_SCHEDULE_B_TEMPLATES.xlsx
@@ -93,14 +93,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000099CC"/>
-        <bgColor rgb="000099CC"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="000099CC"/>
+        <bgColor rgb="000099CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -110,13 +110,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
     </border>
     <border>
       <left style="thin">
@@ -138,36 +144,36 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -632,1214 +638,1225 @@
       <c r="I6" s="1" t="n"/>
       <c r="J6" s="1" t="n"/>
     </row>
-    <row r="7" ht="8" customHeight="1"/>
+    <row r="7" ht="8" customHeight="1">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+    </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  ALL ROLE KPI TEMPLATES (30 ROLES)</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Role ID</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Job Title</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>KPI 1</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>KPI 2</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>KPI 3</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>KPI 4</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>KPI 5</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>PECH-ENG-CTO-001</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>CTO</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>System uptime &gt;99.5%</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Sprint velocity +10%/quarter</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Hire pipeline filled</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Security: 0 critical vulns</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Tech debt &lt;15%</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>PECH-ENG-FS-001</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Full-Stack Engineer</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Feature delivery on sprint</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Code review participation</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>Bug fix turnaround &lt;48h</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>Unit test coverage &gt;80%</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>Documentation updated</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>PECH-ENG-FE-001</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Frontend Engineer</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Page load &lt;2s</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Lighthouse score &gt;90</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Cross-browser compat.</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>Accessibility WCAG AA</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>Component library growth</t>
         </is>
       </c>
-      <c r="J12" s="10" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>PECH-ENG-BE-001</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>Backend Engineer</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>API response &lt;200ms p95</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>Zero downtime deploys</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>Error rate &lt;0.1%</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>Database query optimized</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>API documentation 100%</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>PECH-ENG-IOT-001</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>IoT Engineer</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Device connectivity &gt;98%</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Firmware OTA success &gt;99%</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>Sensor accuracy ±2%</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>Battery life targets met</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>Certification compliance</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>PECH-ENG-MOB-001</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Mobile Engineer</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>App store rating &gt;4.5</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Crash-free rate &gt;99.5%</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>App load &lt;3s</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>Feature parity web/mobile</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>User retention +5%/month</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>PECH-ENG-DEV-001</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>DevOps Engineer</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>CI/CD pipeline &lt;10min</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Infrastructure cost -10%</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>Incident response &lt;15min</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>Backup/restore tested monthly</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I16" s="11" t="inlineStr">
         <is>
           <t>Security patches &lt;24h</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>PECH-ENG-DATA-001</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Sr Data Engineer</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Data pipeline uptime &gt;99%</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Query performance SLA met</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>ML model accuracy targets</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>Data quality score &gt;95%</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>Cost per inference -15%</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J17" s="12" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>PECH-ENG-DATA-002</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Weekly reports on time</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Dashboard uptime &gt;99%</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Insight accuracy verified</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>Stakeholder satisfaction &gt;4/5</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>Self-service adoption +20%</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>PECH-ENG-QA-001</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Test coverage &gt;85%</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Bug escape rate &lt;5%</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>Regression suite pass rate</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>Test automation +20%/qtr</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
         <is>
           <t>Release go/no-go accuracy</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>PECH-DES-UI-001</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>UI/UX Designer</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Design system components</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>User task success &gt;90%</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Prototype turnaround &lt;3d</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>Usability test score &gt;80</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>Brand consistency 100%</t>
         </is>
       </c>
-      <c r="J20" s="10" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>PECH-DES-GRA-001</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Graphic Designer</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Asset turnaround &lt;2d</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>Brand guideline adherence</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>Social media engagement</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>Print quality 100%</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>Template library growth</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>PECH-BIZ-PM-001</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Payments PM</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Product &amp; Business</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>PSSP licence milestones</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Transaction success &gt;99.5%</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Feature adoption rate</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>Stakeholder NPS &gt;8</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>Regulatory compliance 100%</t>
         </is>
       </c>
-      <c r="J22" s="10" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>PECH-BIZ-BD-001</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>BD Lead</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Product &amp; Business</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Pipeline value target</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>Conversion rate &gt;15%</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>Partnership agreements</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>Revenue growth targets</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I23" s="12" t="inlineStr">
         <is>
           <t>Client retention &gt;90%</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J23" s="12" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>PECH-BIZ-MKT-001</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>Market Ops Manager</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Product &amp; Business</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Vendor onboarding target</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>GMV growth monthly</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>Market coverage expansion</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>Vendor satisfaction &gt;4/5</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>Operational cost ratio</t>
         </is>
       </c>
-      <c r="J24" s="10" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>PECH-BIZ-COMP-001</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>Compliance Officer</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Product &amp; Business</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Regulatory filings on time</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>Audit findings resolved</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>Policy update cadence</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>Training completion 100%</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>Zero compliance breaches</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="J25" s="12" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>PECH-OPS-LOG-001</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>Logistics Coordinator</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Delivery SLA &gt;95%</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Cost per delivery -10%</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>Route optimization savings</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>Damage rate &lt;1%</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>Driver utilization &gt;85%</t>
         </is>
       </c>
-      <c r="J26" s="10" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>PECH-OPS-CS-001</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>CS Lead</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>First response &lt;1h</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>Resolution time &lt;24h</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>CSAT score &gt;4.5/5</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>Ticket backlog &lt;20</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>Team training hours/month</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="J27" s="12" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="10" t="n">
+      <c r="A28" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>PECH-OPS-CS-002</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>CS Rep</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Tickets resolved/day &gt;15</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>CSAT per agent &gt;4/5</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>First contact resolution &gt;70%</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>Knowledge base updates</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>Escalation rate &lt;10%</t>
         </is>
       </c>
-      <c r="J28" s="10" t="inlineStr">
+      <c r="J28" s="11" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>PECH-OPS-FIN-001</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>Finance Officer</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Books closed by 5th</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>Reconciliation accuracy</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>Expense report turnaround</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>Audit-ready at all times</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>Cash flow forecast accuracy</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="n">
+      <c r="A30" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
-      <c r="J30" s="12" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
+      <c r="I30" s="13" t="n"/>
+      <c r="J30" s="13" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n">
+      <c r="A31" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
-      <c r="H31" s="12" t="n"/>
-      <c r="I31" s="12" t="n"/>
-      <c r="J31" s="12" t="n"/>
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="13" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="13" t="n"/>
+      <c r="H31" s="13" t="n"/>
+      <c r="I31" s="13" t="n"/>
+      <c r="J31" s="13" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="n">
+      <c r="A32" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="12" t="n"/>
-      <c r="J32" s="12" t="n"/>
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="13" t="n"/>
+      <c r="H32" s="13" t="n"/>
+      <c r="I32" s="13" t="n"/>
+      <c r="J32" s="13" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n">
+      <c r="A33" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="12" t="n"/>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="12" t="n"/>
-      <c r="J33" s="12" t="n"/>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="13" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="13" t="n"/>
+      <c r="H33" s="13" t="n"/>
+      <c r="I33" s="13" t="n"/>
+      <c r="J33" s="13" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="n">
+      <c r="A34" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="12" t="n"/>
-      <c r="H34" s="12" t="n"/>
-      <c r="I34" s="12" t="n"/>
-      <c r="J34" s="12" t="n"/>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="13" t="n"/>
+      <c r="D34" s="13" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
+      <c r="G34" s="13" t="n"/>
+      <c r="H34" s="13" t="n"/>
+      <c r="I34" s="13" t="n"/>
+      <c r="J34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="n">
+      <c r="A35" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="12" t="n"/>
-      <c r="H35" s="12" t="n"/>
-      <c r="I35" s="12" t="n"/>
-      <c r="J35" s="12" t="n"/>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="13" t="n"/>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="13" t="n"/>
+      <c r="H35" s="13" t="n"/>
+      <c r="I35" s="13" t="n"/>
+      <c r="J35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="n">
+      <c r="A36" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="12" t="n"/>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="12" t="n"/>
-      <c r="G36" s="12" t="n"/>
-      <c r="H36" s="12" t="n"/>
-      <c r="I36" s="12" t="n"/>
-      <c r="J36" s="12" t="n"/>
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="13" t="n"/>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="13" t="n"/>
+      <c r="G36" s="13" t="n"/>
+      <c r="H36" s="13" t="n"/>
+      <c r="I36" s="13" t="n"/>
+      <c r="J36" s="13" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="n">
+      <c r="A37" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="12" t="n"/>
-      <c r="H37" s="12" t="n"/>
-      <c r="I37" s="12" t="n"/>
-      <c r="J37" s="12" t="n"/>
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="13" t="n"/>
+      <c r="H37" s="13" t="n"/>
+      <c r="I37" s="13" t="n"/>
+      <c r="J37" s="13" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="n">
+      <c r="A38" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="12" t="n"/>
-      <c r="H38" s="12" t="n"/>
-      <c r="I38" s="12" t="n"/>
-      <c r="J38" s="12" t="n"/>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="13" t="n"/>
+      <c r="H38" s="13" t="n"/>
+      <c r="I38" s="13" t="n"/>
+      <c r="J38" s="13" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="n">
+      <c r="A39" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="12" t="n"/>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="12" t="n"/>
-      <c r="H39" s="12" t="n"/>
-      <c r="I39" s="12" t="n"/>
-      <c r="J39" s="12" t="n"/>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="13" t="n"/>
+      <c r="D39" s="13" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="13" t="n"/>
+      <c r="H39" s="13" t="n"/>
+      <c r="I39" s="13" t="n"/>
+      <c r="J39" s="13" t="n"/>
     </row>
     <row r="41" ht="3" customHeight="1">
       <c r="A41" s="5" t="n"/>
@@ -1853,21 +1870,21 @@
       <c r="I41" s="5" t="n"/>
       <c r="J41" s="5" t="n"/>
     </row>
-    <row r="42">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-      <c r="B42" s="14" t="n"/>
-      <c r="C42" s="14" t="n"/>
-      <c r="D42" s="14" t="n"/>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="14" t="n"/>
-      <c r="G42" s="14" t="n"/>
-      <c r="H42" s="14" t="n"/>
-      <c r="I42" s="14" t="n"/>
-      <c r="J42" s="14" t="n"/>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
+      <c r="J42" s="7" t="n"/>
     </row>
     <row r="43" ht="3" customHeight="1">
       <c r="A43" s="1" t="n"/>
